--- a/src/attributions/attributions_ig_traj_398.xlsx
+++ b/src/attributions/attributions_ig_traj_398.xlsx
@@ -1571,7 +1571,7 @@
         <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>0.08440094860274742</v>
+        <v>0.2164762892367559</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -1580,16 +1580,16 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006301232016214748</v>
+        <v>0.02865854774097118</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.023058997692632</v>
+        <v>-0.08281957987820772</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -1598,7 +1598,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02410958120406008</v>
+        <v>0.1908629465216258</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1607,25 +1607,25 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.01048314705891322</v>
+        <v>-0.01572764376228769</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01361638305075547</v>
+        <v>0.03566737835342478</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.001015161706168448</v>
+        <v>0.07426442093493069</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1634,52 +1634,52 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.01379489527403371</v>
+        <v>-0.03453488020845408</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0148168897488952</v>
+        <v>0.02972562125555643</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB3" t="n">
         <v>-0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.01858549608963934</v>
+        <v>-0.02719938586015185</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0211860113128844</v>
+        <v>-0.08598330768971404</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.004967328903196723</v>
+        <v>0.02223553306228508</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ3" t="n">
         <v>-0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.01502966448191032</v>
+        <v>0.09608251568642448</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
@@ -1688,25 +1688,25 @@
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.0111951483356003</v>
+        <v>0.03376307498700013</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.02190350035075703</v>
+        <v>-0.07465685503518948</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS3" t="n">
         <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.1116907066557526</v>
+        <v>0.3183009703359483</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1715,25 +1715,25 @@
         <v>-0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.03529922869308269</v>
+        <v>-0.09214651885912487</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.009219038599016401</v>
+        <v>-0.1479082204343689</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA3" t="n">
         <v>-0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.01269189094310904</v>
+        <v>-0.01552810858986653</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
@@ -1742,25 +1742,25 @@
         <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.01535720271545067</v>
+        <v>-0.04099926423954624</v>
       </c>
       <c r="BH3" t="n">
-        <v>-0.006462891835168776</v>
+        <v>-0.01142223692322303</v>
       </c>
       <c r="BI3" t="n">
         <v>-0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.04790362678193091</v>
+        <v>0.005172073581089585</v>
       </c>
       <c r="BN3" t="n">
         <v>-0</v>
@@ -1769,43 +1769,43 @@
         <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.03260433707359189</v>
+        <v>0.09362598925653463</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.006920442415234446</v>
+        <v>0.08272657406209939</v>
       </c>
       <c r="BR3" t="n">
         <v>-0</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
         <v>-0</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.04836946211526206</v>
+        <v>0.264408231512788</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.01535612493247544</v>
+        <v>0.02149253060581806</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.0350746895527475</v>
+        <v>-0.06156143011705188</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC3" t="n">
         <v>-0</v>
@@ -1814,130 +1814,130 @@
         <v>-0</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.01317841311922432</v>
+        <v>-0.09456656783475212</v>
       </c>
       <c r="CF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.00731613056990536</v>
+        <v>-0.01132790193205662</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.01765935675925932</v>
+        <v>0.07001351162924883</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK3" t="n">
         <v>0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.01193816572265544</v>
+        <v>-0.05496466635137409</v>
       </c>
       <c r="CO3" t="n">
         <v>0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.005360719481054511</v>
+        <v>0.1425717890186766</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0.038486155215571</v>
+        <v>-0.01320986531814182</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
         <v>0</v>
       </c>
       <c r="CW3" t="n">
-        <v>-0.006463941637820793</v>
+        <v>-0.08611248084667812</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY3" t="n">
         <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>-0.006921411360625258</v>
+        <v>0.005766889589526787</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.02148298442827631</v>
+        <v>0.08079865219440578</v>
       </c>
       <c r="DB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD3" t="n">
         <v>0</v>
       </c>
       <c r="DE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.002594924311519506</v>
+        <v>-0.05890120067865605</v>
       </c>
       <c r="DG3" t="n">
         <v>0</v>
       </c>
       <c r="DH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.02195836511720325</v>
+        <v>-0.06910155075953452</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.02011756530066638</v>
+        <v>0.1199680947280107</v>
       </c>
       <c r="DK3" t="n">
         <v>0</v>
       </c>
       <c r="DL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN3" t="n">
         <v>-0</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.007437342090832054</v>
+        <v>-0.0760639095190558</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.02421280068380516</v>
+        <v>-0.01168178046789523</v>
       </c>
       <c r="DS3" t="n">
-        <v>-0.009602765535947825</v>
+        <v>0.02143307162255113</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU3" t="n">
         <v>-0</v>
@@ -1949,25 +1949,25 @@
         <v>-0</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.03332275208414679</v>
+        <v>-0.01372261064576589</v>
       </c>
       <c r="DY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ3" t="n">
         <v>0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.04525641478907282</v>
+        <v>-0.0933676300168045</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.01334943503428463</v>
+        <v>0.03156473468473874</v>
       </c>
       <c r="EC3" t="n">
         <v>-0</v>
       </c>
       <c r="ED3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE3" t="n">
         <v>-0</v>
@@ -1976,76 +1976,76 @@
         <v>-0</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.003130600432085098</v>
+        <v>-0.006784863029969729</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.01128372977112815</v>
+        <v>-0.03735894440196746</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.002565153878982001</v>
+        <v>-0.0002289979401020033</v>
       </c>
       <c r="EL3" t="n">
         <v>-0</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN3" t="n">
         <v>-0</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0.004782190689853828</v>
+        <v>-0.05392726620853482</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER3" t="n">
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0.02904318892618387</v>
+        <v>-0.1599719509304359</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0.07290375372660021</v>
+        <v>-0.1508796470932954</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX3" t="n">
         <v>-0</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.001376947256045571</v>
+        <v>-0.1005106013280339</v>
       </c>
       <c r="EZ3" t="n">
         <v>-0</v>
       </c>
       <c r="FA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0.006675613461328673</v>
+        <v>-0.01694727412102287</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.02148986081005339</v>
+        <v>0.06070648279906386</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE3" t="n">
         <v>0</v>
@@ -2057,64 +2057,64 @@
         <v>0</v>
       </c>
       <c r="FH3" t="n">
-        <v>-0.02584558021082215</v>
+        <v>-0.1023601447096605</v>
       </c>
       <c r="FI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ3" t="n">
         <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.0501189435944211</v>
+        <v>0.06181754949276135</v>
       </c>
       <c r="FL3" t="n">
-        <v>-0.007157666471593306</v>
+        <v>0.06268809876329341</v>
       </c>
       <c r="FM3" t="n">
         <v>0</v>
       </c>
       <c r="FN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO3" t="n">
         <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ3" t="n">
-        <v>-0.006242512191815478</v>
+        <v>0.01137943826666585</v>
       </c>
       <c r="FR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS3" t="n">
         <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0.01442186785084242</v>
+        <v>0.006835493193216548</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.03589552225207911</v>
+        <v>-0.1061838881410321</v>
       </c>
       <c r="FV3" t="n">
         <v>-0</v>
       </c>
       <c r="FW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ3" t="n">
-        <v>-0.03485961479116229</v>
+        <v>-0.03119177234938971</v>
       </c>
       <c r="GA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB3" t="n">
         <v>-0</v>
@@ -2123,13 +2123,13 @@
         <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0.01029730559743866</v>
+        <v>-0.006913452727081655</v>
       </c>
       <c r="GE3" t="n">
         <v>0</v>
       </c>
       <c r="GF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG3" t="n">
         <v>0</v>
@@ -2140,16 +2140,16 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.3836454946861937</v>
+        <v>0.2518497289017765</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.09308640439234685</v>
+        <v>-0.08233051517901951</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.09126931922489831</v>
+        <v>-0.06271230314983375</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2161,25 +2161,25 @@
         <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.210792888489997</v>
+        <v>0.195602938753753</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.01053419533937284</v>
+        <v>-0.01474751490804043</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0867047139124897</v>
+        <v>-0.06768671686667976</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4" t="n">
         <v>-0</v>
@@ -2188,85 +2188,85 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1015832405763104</v>
+        <v>0.06250394016693496</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.01216169466055212</v>
+        <v>-0.04156178356172571</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.02084116873993643</v>
+        <v>-0.04246623968250413</v>
       </c>
       <c r="X4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.05300023826135532</v>
+        <v>-0.02124719742075131</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.03339238211276682</v>
+        <v>-0.02892282179926652</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.01723238380516949</v>
+        <v>-0.08024241410235736</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.07670741721586681</v>
+        <v>0.1192873529119212</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.05413878649414011</v>
+        <v>-0.04091040149933428</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.05701637730298302</v>
+        <v>0.04630621857309625</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
@@ -2275,16 +2275,16 @@
         <v>-0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.4427223953998405</v>
+        <v>0.2815547344171557</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>-0.04646642857068213</v>
+        <v>-0.09868352290342439</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1329060763358925</v>
+        <v>-0.1327914926004385</v>
       </c>
       <c r="AY4" t="n">
         <v>-0</v>
@@ -2293,25 +2293,25 @@
         <v>-0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.03400943943779196</v>
+        <v>-0.03504135337230775</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.02534623509905633</v>
+        <v>-0.003237285330413054</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.1180790012163503</v>
+        <v>-0.02893202707356115</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
@@ -2320,7 +2320,7 @@
         <v>-0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
         <v>-0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.0642005645735087</v>
+        <v>0.006083692992628001</v>
       </c>
       <c r="BN4" t="n">
         <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.1180472702840968</v>
+        <v>0.0469766558098366</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.06891407242255128</v>
+        <v>0.06535272305059818</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
         <v>-0</v>
@@ -2356,19 +2356,19 @@
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.2633232398277967</v>
+        <v>0.2582309604799025</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX4" t="n">
-        <v>-0.02686356766011045</v>
+        <v>-0.1066708778375603</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.005495462956675912</v>
+        <v>-0.05187525754626474</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
@@ -2383,46 +2383,46 @@
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.1034741295069625</v>
+        <v>-0.1110794610575873</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.02416261855858568</v>
+        <v>0.09315809021221585</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.003898167020707994</v>
+        <v>0.01411305853480858</v>
       </c>
       <c r="CI4" t="n">
         <v>-0</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.02658208272831469</v>
+        <v>-0.08589463838565617</v>
       </c>
       <c r="CO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0.08918989969678466</v>
+        <v>0.1012071446596841</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.1571664544498456</v>
+        <v>0.05314069476304657</v>
       </c>
       <c r="CR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS4" t="n">
         <v>-0</v>
@@ -2431,55 +2431,55 @@
         <v>-0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
         <v>0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.08144128162828022</v>
+        <v>-0.1137075784053626</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.06005848111843998</v>
+        <v>0.1027128494739166</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.00415226073250238</v>
+        <v>0.02550220495358468</v>
       </c>
       <c r="DA4" t="n">
         <v>0</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC4" t="n">
         <v>-0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.06022559081736251</v>
+        <v>-0.08699566741599259</v>
       </c>
       <c r="DG4" t="n">
         <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.06016741528140626</v>
+        <v>0.07129478454900129</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.01145750903933057</v>
+        <v>-0.04304888994926237</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL4" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.06435292901561054</v>
+        <v>-0.06019451471774653</v>
       </c>
       <c r="DP4" t="n">
         <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0.05160751814156096</v>
+        <v>0.01872988672452108</v>
       </c>
       <c r="DR4" t="n">
-        <v>-0.0156853536233725</v>
+        <v>-0.0499077842460988</v>
       </c>
       <c r="DS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT4" t="n">
         <v>-0</v>
@@ -2518,76 +2518,76 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.03949729069093381</v>
+        <v>0.04300242781063796</v>
       </c>
       <c r="DY4" t="n">
         <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>-0.02606983047856969</v>
+        <v>0.04755738930798666</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.01980471277938065</v>
+        <v>-0.03863072148464018</v>
       </c>
       <c r="EB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.05296651233063275</v>
+        <v>-0.05923595534005997</v>
       </c>
       <c r="EH4" t="n">
         <v>0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.07928953146220015</v>
+        <v>0.08592441651814488</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.04595607892472457</v>
+        <v>0.01504749882613203</v>
       </c>
       <c r="EK4" t="n">
         <v>-0</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.08232238644166973</v>
+        <v>-0.07160861652999718</v>
       </c>
       <c r="EQ4" t="n">
         <v>0</v>
       </c>
       <c r="ER4" t="n">
-        <v>-0.08579133588256346</v>
+        <v>-0.08650022407468295</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.02961414585450922</v>
+        <v>-0.004484503486656416</v>
       </c>
       <c r="ET4" t="n">
         <v>-0</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
         <v>0</v>
@@ -2599,43 +2599,43 @@
         <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.09343115600467349</v>
+        <v>-0.1287222887383165</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.04793870477197697</v>
+        <v>0.1018437090983317</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.02160916754672522</v>
+        <v>0.009492282016400934</v>
       </c>
       <c r="FC4" t="n">
         <v>-0</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
         <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
         <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.008394309925113161</v>
+        <v>-0.05851573523181524</v>
       </c>
       <c r="FI4" t="n">
         <v>-0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.07032942214801258</v>
+        <v>0.04242200899126504</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.003112923766127958</v>
+        <v>0.009357705578557935</v>
       </c>
       <c r="FL4" t="n">
         <v>0</v>
@@ -2647,25 +2647,25 @@
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.01379251158395955</v>
+        <v>0.01862896346170853</v>
       </c>
       <c r="FR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.007932420252398077</v>
+        <v>0.1116728873713191</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.04251077813877549</v>
+        <v>-0.01685798325619414</v>
       </c>
       <c r="FU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
@@ -2677,31 +2677,31 @@
         <v>0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.002780105288052959</v>
+        <v>-0.07523144747492466</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
-        <v>-0.02324492507080232</v>
+        <v>0.02577953596268341</v>
       </c>
       <c r="GC4" t="n">
         <v>0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE4" t="n">
         <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -3275,46 +3275,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2734709250969927</v>
+        <v>0.08140609752185365</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.01656279059935801</v>
+        <v>-0.0123105041373893</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.03532206335922913</v>
+        <v>-0.02480548806082556</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1279032204509686</v>
+        <v>0.07213823977898304</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01315272266921724</v>
+        <v>0.01109083203845049</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.03663248511554056</v>
+        <v>-0.02748406940162639</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -3326,25 +3326,25 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.04800056615232391</v>
+        <v>0.02445247382522028</v>
       </c>
       <c r="U6" t="n">
         <v>-0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0178133636294931</v>
+        <v>-0.003262951194973739</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03847434953600808</v>
+        <v>-0.0005857399775602662</v>
       </c>
       <c r="X6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>-0</v>
@@ -3353,49 +3353,49 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.04069224824287786</v>
+        <v>-0.01022805468993622</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.004247861677934876</v>
+        <v>-0.03194805655063504</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.002071873351593078</v>
+        <v>-0.03341708547299666</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>-0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.008973734130676536</v>
+        <v>0.03857323780465166</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.01936192805655749</v>
+        <v>-0.005340049209556334</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.03829707601787757</v>
+        <v>0.03385535484576191</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
@@ -3404,61 +3404,61 @@
         <v>-0</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT6" t="n">
         <v>-0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.2861617997569122</v>
+        <v>0.1044243312929407</v>
       </c>
       <c r="AV6" t="n">
         <v>-0</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.03121390016164712</v>
+        <v>-0.004404166456230931</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.07216275915364746</v>
+        <v>-0.05011751614746766</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
         <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.04503182824325454</v>
+        <v>-0.02461769493231403</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.04411623881288795</v>
+        <v>-0.006878787373987873</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.04625351565820888</v>
+        <v>-0.009546686041555761</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
@@ -3467,19 +3467,19 @@
         <v>-0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.1046970549562724</v>
+        <v>0.02178936881422825</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.02406344708078152</v>
+        <v>0.01813712491414362</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.1121315592084563</v>
+        <v>0.04599707834629407</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR6" t="n">
         <v>0</v>
@@ -3494,25 +3494,25 @@
         <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.1544560284916798</v>
+        <v>0.09962966525545841</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.03063601793053538</v>
+        <v>-0.02718217741694234</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.0329844386198656</v>
+        <v>-0.004898568773132722</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA6" t="n">
         <v>-0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC6" t="n">
         <v>-0</v>
@@ -3521,49 +3521,49 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.0664722330739969</v>
+        <v>-0.03132667851373561</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.002336196207446382</v>
+        <v>0.02831276420597939</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.0009873776695465788</v>
+        <v>0.01579087424411853</v>
       </c>
       <c r="CI6" t="n">
         <v>-0</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
       </c>
       <c r="CL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM6" t="n">
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.0554910861128541</v>
+        <v>-0.04255375168761956</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0.04510073205745924</v>
+        <v>0.03216450723287445</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.06701911248464423</v>
+        <v>0.02044367849043528</v>
       </c>
       <c r="CR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT6" t="n">
         <v>-0</v>
@@ -3572,19 +3572,19 @@
         <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.04731519436655857</v>
+        <v>-0.03001191178851162</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.009277005982134384</v>
+        <v>0.03109765950119448</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.002130324633390895</v>
+        <v>0.01730544956101739</v>
       </c>
       <c r="DA6" t="n">
         <v>0</v>
@@ -3593,82 +3593,82 @@
         <v>0</v>
       </c>
       <c r="DC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD6" t="n">
         <v>0</v>
       </c>
       <c r="DE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.01281296907707961</v>
+        <v>-0.0003530579609699029</v>
       </c>
       <c r="DG6" t="n">
         <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.06455568655513604</v>
+        <v>0.00775070310908386</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.004124579681731411</v>
+        <v>-0.004629738587465532</v>
       </c>
       <c r="DJ6" t="n">
         <v>-0</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL6" t="n">
         <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.07935816727173679</v>
+        <v>-0.02844047521840455</v>
       </c>
       <c r="DP6" t="n">
         <v>0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0.01017228502418743</v>
+        <v>-0.01672987588492511</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.01798896414493234</v>
+        <v>-0.01387124506396278</v>
       </c>
       <c r="DS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU6" t="n">
         <v>-0</v>
       </c>
       <c r="DV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW6" t="n">
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.009030765607100652</v>
+        <v>0.03209314111523257</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>-0.005132272163888154</v>
+        <v>0.01608581067548913</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.02478333135251647</v>
+        <v>-0.04480298634998275</v>
       </c>
       <c r="EB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC6" t="n">
         <v>0</v>
@@ -3677,22 +3677,22 @@
         <v>0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.04368663634617597</v>
+        <v>0.005421771707580983</v>
       </c>
       <c r="EH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.004234668626125668</v>
+        <v>0.02642971959190482</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.04200686467530815</v>
+        <v>0.02933604740755174</v>
       </c>
       <c r="EK6" t="n">
         <v>-0</v>
@@ -3701,7 +3701,7 @@
         <v>-0</v>
       </c>
       <c r="EM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN6" t="n">
         <v>-0</v>
@@ -3710,25 +3710,25 @@
         <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.03240650373466255</v>
+        <v>-0.02397694671832921</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.006863686414720195</v>
+        <v>0.03196819175104409</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.02601500813307979</v>
+        <v>-0.002586145597492224</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW6" t="n">
         <v>-0</v>
@@ -3737,16 +3737,16 @@
         <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.04622187686743717</v>
+        <v>-0.03582365406751863</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.001232189368747713</v>
+        <v>0.03740772895648617</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.01284830728024838</v>
+        <v>0.008867091182436263</v>
       </c>
       <c r="FC6" t="n">
         <v>-0</v>
@@ -3761,55 +3761,55 @@
         <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.00566408038452801</v>
+        <v>-0.001956882938163554</v>
       </c>
       <c r="FI6" t="n">
         <v>-0</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.004449340401770054</v>
+        <v>-0.00557517628483773</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.03073844117544607</v>
+        <v>-0.01624301893839215</v>
       </c>
       <c r="FL6" t="n">
         <v>-0</v>
       </c>
       <c r="FM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.03657807896288052</v>
+        <v>0.01493662460100276</v>
       </c>
       <c r="FR6" t="n">
         <v>0</v>
       </c>
       <c r="FS6" t="n">
-        <v>-0.02271692819191403</v>
+        <v>0.03138417247735515</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.0123352386926605</v>
+        <v>-0.04311731036641902</v>
       </c>
       <c r="FU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX6" t="n">
         <v>0</v>
@@ -3818,28 +3818,28 @@
         <v>-0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.01065250289943449</v>
+        <v>-0.01157602398764621</v>
       </c>
       <c r="GA6" t="n">
         <v>-0</v>
       </c>
       <c r="GB6" t="n">
-        <v>-0.02806435739250662</v>
+        <v>-0.002583475568405969</v>
       </c>
       <c r="GC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE6" t="n">
         <v>-0</v>
       </c>
       <c r="GF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3847,19 +3847,19 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.216864286648438</v>
+        <v>0.2401875373297066</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01143035383736961</v>
+        <v>-0.03026017235342797</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1299524673054379</v>
+        <v>-0.08213439753196111</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1368045076915777</v>
+        <v>0.2868627559761219</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -3883,16 +3883,16 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.003815716621475814</v>
+        <v>-0.07184760082926309</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.08273774947516563</v>
+        <v>-0.04126354331541009</v>
       </c>
       <c r="P7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -3901,46 +3901,46 @@
         <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.00789361096447313</v>
+        <v>0.05447393815533829</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.02680369112178394</v>
+        <v>-0.05795817870303016</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.008808615740041039</v>
+        <v>-0.006192065423164592</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.02868377239076729</v>
+        <v>-0.02831374793371106</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.01815066834270471</v>
+        <v>-0.09699800942769402</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.0100880673271035</v>
+        <v>-0.006654803524024554</v>
       </c>
       <c r="AH7" t="n">
         <v>-0</v>
@@ -3949,13 +3949,13 @@
         <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.0119086573341829</v>
+        <v>0.05679030617802436</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
@@ -3964,13 +3964,13 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.02631743465136811</v>
+        <v>0.01855817953199189</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.05144471721620988</v>
+        <v>-0.02962359920687286</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>-0</v>
@@ -3979,28 +3979,28 @@
         <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1664629257209929</v>
+        <v>0.261334934571314</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.007490108327991972</v>
+        <v>-0.1061981735472189</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.07037471332052052</v>
+        <v>-0.05716395639199387</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
         <v>0</v>
@@ -4009,7 +4009,7 @@
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.06876721579801763</v>
+        <v>-0.01118597009248665</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -4018,64 +4018,64 @@
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.02041077999653357</v>
+        <v>-0.05554465462499766</v>
       </c>
       <c r="BH7" t="n">
-        <v>-0.04818071897400177</v>
+        <v>-0.03193092384132216</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.0785418338068771</v>
+        <v>0.0287826876630447</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO7" t="n">
         <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.04793264121558687</v>
+        <v>0.0550014348455951</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.008959182921481902</v>
+        <v>-0.005053128626687064</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.09022961512010096</v>
+        <v>0.2201266732704013</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
         <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.02042726362581106</v>
+        <v>-0.03825210933324173</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0.01108576901486806</v>
+        <v>-0.05236537929448221</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
@@ -4090,73 +4090,73 @@
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.04836720372375943</v>
+        <v>-0.0968901966473239</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.01086833962051203</v>
+        <v>0.01071700162886377</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.03743702576942352</v>
+        <v>0.05205497462267116</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.02971526368426385</v>
+        <v>-0.1298106042711855</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.02642603967475154</v>
+        <v>0.09337465809144994</v>
       </c>
       <c r="CR7" t="n">
-        <v>-0.03602061742008963</v>
+        <v>0.07084996670267218</v>
       </c>
       <c r="CS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.0321256622139813</v>
+        <v>-0.09231844702246082</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.01058375380611812</v>
+        <v>0.00213741601178368</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.03563671799138315</v>
+        <v>0.05172828088877529</v>
       </c>
       <c r="DB7" t="n">
         <v>0</v>
@@ -4171,19 +4171,19 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.009877442954452803</v>
+        <v>-0.00937532228769845</v>
       </c>
       <c r="DG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.002507159241598074</v>
+        <v>-0.02991382622413972</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.003364767616034653</v>
+        <v>0.02141307855574455</v>
       </c>
       <c r="DK7" t="n">
         <v>0</v>
@@ -4192,28 +4192,28 @@
         <v>-0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.03535493925990531</v>
+        <v>-0.06921304259013916</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
         <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.01521037323716219</v>
+        <v>0.01890155759608228</v>
       </c>
       <c r="DS7" t="n">
-        <v>-0.01696931342078842</v>
+        <v>-0.01660274913313186</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
         <v>-0</v>
@@ -4225,34 +4225,34 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.009858814659470916</v>
+        <v>0.04883796419535768</v>
       </c>
       <c r="DY7" t="n">
         <v>0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.02470046319794069</v>
+        <v>0.01943547525399707</v>
       </c>
       <c r="EB7" t="n">
-        <v>-0.004913031991203256</v>
+        <v>-0.08675575577320847</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
         <v>-0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.02156246365496496</v>
+        <v>-0.005695596980942391</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
@@ -4261,10 +4261,10 @@
         <v>0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.004618937855440788</v>
+        <v>-0.03878915405184136</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.02568581511987382</v>
+        <v>0.02560830986891607</v>
       </c>
       <c r="EL7" t="n">
         <v>-0</v>
@@ -4273,67 +4273,67 @@
         <v>-0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.03108273694669908</v>
+        <v>-0.01312620809079758</v>
       </c>
       <c r="EQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER7" t="n">
         <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.01545850338242516</v>
+        <v>-0.06173983309434336</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.06339073702808</v>
+        <v>0.05335374202620816</v>
       </c>
       <c r="EU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX7" t="n">
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.03536169564870971</v>
+        <v>-0.1049485543590355</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
         <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.003466847984897275</v>
+        <v>-0.0101455583610313</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.04038560225881216</v>
+        <v>0.04598739825220299</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
         <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.006528883595991354</v>
+        <v>-0.09187415325157627</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
@@ -4342,37 +4342,37 @@
         <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.02583508315812875</v>
+        <v>0.06284448746368552</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.01930090200584055</v>
+        <v>0.03387466350789974</v>
       </c>
       <c r="FM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.02471760914341506</v>
+        <v>0.03593646511911317</v>
       </c>
       <c r="FR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.03102413282885879</v>
+        <v>-0.0247216178896063</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.002086133861337379</v>
+        <v>0.000714977276940657</v>
       </c>
       <c r="FV7" t="n">
         <v>-0</v>
@@ -4381,28 +4381,28 @@
         <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.02898713024414378</v>
+        <v>-0.01783075370228495</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
         <v>-0</v>
       </c>
       <c r="GC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0.02474126999421371</v>
+        <v>0.0125149453572319</v>
       </c>
       <c r="GE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF7" t="n">
         <v>-0</v>
@@ -4419,13 +4419,13 @@
         <v>-0</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2032110328155803</v>
+        <v>-0.1325594223989602</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3190568812369344</v>
+        <v>0.04716467549884247</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.05429625442983015</v>
+        <v>-0.1246722328513074</v>
       </c>
       <c r="F8" t="n">
         <v>-0</v>
@@ -4434,7 +4434,7 @@
         <v>-0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I8" t="n">
         <v>-0</v>
@@ -4443,70 +4443,70 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.08961352545669121</v>
+        <v>-0.05073577436391199</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3100683697935187</v>
+        <v>0.00258796072023053</v>
       </c>
       <c r="N8" t="n">
-        <v>0.06511804859062365</v>
+        <v>-0.1083655832389034</v>
       </c>
       <c r="O8" t="n">
         <v>-0</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R8" t="n">
         <v>-0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.05085837336626176</v>
+        <v>-0.04301557651423852</v>
       </c>
       <c r="V8" t="n">
-        <v>0.07921251372394666</v>
+        <v>0.06795203000450944</v>
       </c>
       <c r="W8" t="n">
-        <v>0.00433336302137876</v>
+        <v>0.01312511275929936</v>
       </c>
       <c r="X8" t="n">
         <v>-0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.002931917981202756</v>
+        <v>-0.01304587879243492</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.06879100453733288</v>
+        <v>-0.08610650824000347</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.0628711626260202</v>
+        <v>-0.08191033327933639</v>
       </c>
       <c r="AG8" t="n">
         <v>-0</v>
@@ -4521,46 +4521,46 @@
         <v>-0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0.006763591541608337</v>
+        <v>-0.07442510078070523</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.05059258514820261</v>
+        <v>0.08711976791565619</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.06457882307670043</v>
+        <v>-0.01554159091030439</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU8" t="n">
         <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.1223823151151266</v>
+        <v>-0.123658619126715</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.2056988821529689</v>
+        <v>0.2272442765999307</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.1871657033850715</v>
+        <v>-0.152341257452049</v>
       </c>
       <c r="AY8" t="n">
         <v>0</v>
@@ -4581,13 +4581,13 @@
         <v>-0</v>
       </c>
       <c r="BE8" t="n">
-        <v>-0.02858878518267212</v>
+        <v>0.005963700732391843</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.03572740283763775</v>
+        <v>-0.2107211725446221</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.027345551681121</v>
+        <v>-0.07274198266402274</v>
       </c>
       <c r="BH8" t="n">
         <v>-0</v>
@@ -4596,139 +4596,139 @@
         <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
         <v>-0</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.05712993816438941</v>
+        <v>0.08317886143818773</v>
       </c>
       <c r="BO8" t="n">
-        <v>-0.03109150493877358</v>
+        <v>0.08415005615963768</v>
       </c>
       <c r="BP8" t="n">
-        <v>-0.1639489864863477</v>
+        <v>0.1634927281065804</v>
       </c>
       <c r="BQ8" t="n">
         <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
         <v>-0</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW8" t="n">
-        <v>-0.1400013863853458</v>
+        <v>-0.122026836889867</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.1631511956926911</v>
+        <v>0.264062569743008</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.1279525081983088</v>
+        <v>-0.0294335673250368</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
       </c>
       <c r="CB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE8" t="n">
         <v>0</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.07146808793342588</v>
+        <v>0.07930327785405844</v>
       </c>
       <c r="CG8" t="n">
-        <v>-0.07203126060285131</v>
+        <v>-0.001694650622248425</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.0206241764028169</v>
+        <v>0.03677892767944285</v>
       </c>
       <c r="CI8" t="n">
         <v>-0</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL8" t="n">
         <v>0</v>
       </c>
       <c r="CM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.02729911983137989</v>
+        <v>0.03464651259280589</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.05216365985622556</v>
+        <v>0.01882222322402049</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.117976936062134</v>
+        <v>0.08696259125795566</v>
       </c>
       <c r="CR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS8" t="n">
         <v>-0</v>
       </c>
       <c r="CT8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU8" t="n">
         <v>0</v>
       </c>
       <c r="CV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW8" t="n">
         <v>-0</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.04901854122519995</v>
+        <v>0.05887245181037391</v>
       </c>
       <c r="CY8" t="n">
-        <v>-0.06228202072978322</v>
+        <v>0.003160282152152801</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.02958642233572432</v>
+        <v>0.05825756420299363</v>
       </c>
       <c r="DA8" t="n">
         <v>0</v>
       </c>
       <c r="DB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC8" t="n">
         <v>-0</v>
@@ -4740,19 +4740,19 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.01177987150223061</v>
+        <v>0.03332470984371121</v>
       </c>
       <c r="DH8" t="n">
-        <v>-0.07528141296932805</v>
+        <v>-0.0356535392973737</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.005031694126741959</v>
+        <v>-0.005266680333968312</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
         <v>-0</v>
       </c>
       <c r="DM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO8" t="n">
         <v>0</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.05065129266407726</v>
+        <v>-0.004642581444389051</v>
       </c>
       <c r="DQ8" t="n">
-        <v>-0.03145547851016951</v>
+        <v>-0.04282845842158851</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0748144822362288</v>
+        <v>0.1159381680369495</v>
       </c>
       <c r="DS8" t="n">
         <v>-0</v>
@@ -4785,34 +4785,34 @@
         <v>-0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
         <v>-0</v>
       </c>
       <c r="DW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY8" t="n">
-        <v>-0.004826673691619097</v>
+        <v>-0.05445694675157786</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.02987060268187951</v>
+        <v>-0.01607823152207737</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.03107778838155132</v>
+        <v>-0.1177182216379851</v>
       </c>
       <c r="EB8" t="n">
         <v>-0</v>
       </c>
       <c r="EC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE8" t="n">
         <v>0</v>
@@ -4821,22 +4821,22 @@
         <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.08010696090910485</v>
+        <v>0.02620072231713719</v>
       </c>
       <c r="EI8" t="n">
-        <v>-0.1093417736268444</v>
+        <v>0.08453625132806943</v>
       </c>
       <c r="EJ8" t="n">
-        <v>-0.04631693243945469</v>
+        <v>-0.01309581458692939</v>
       </c>
       <c r="EK8" t="n">
         <v>0</v>
       </c>
       <c r="EL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM8" t="n">
         <v>0</v>
@@ -4845,55 +4845,55 @@
         <v>0</v>
       </c>
       <c r="EO8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.02407575698732089</v>
+        <v>-0.001230191804396248</v>
       </c>
       <c r="ER8" t="n">
-        <v>-0.04236544088497952</v>
+        <v>-0.01679993658297675</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.03806780649318995</v>
+        <v>-0.008531539036894452</v>
       </c>
       <c r="ET8" t="n">
         <v>-0</v>
       </c>
       <c r="EU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV8" t="n">
         <v>-0</v>
       </c>
       <c r="EW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY8" t="n">
         <v>0</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.06522939512771149</v>
+        <v>0.05943215453955882</v>
       </c>
       <c r="FA8" t="n">
-        <v>-0.07109526174167904</v>
+        <v>-0.02386832860373377</v>
       </c>
       <c r="FB8" t="n">
-        <v>-0.039274156393684</v>
+        <v>0.04234261076123017</v>
       </c>
       <c r="FC8" t="n">
         <v>-0</v>
       </c>
       <c r="FD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF8" t="n">
         <v>0</v>
@@ -4902,25 +4902,25 @@
         <v>-0</v>
       </c>
       <c r="FH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.028934240092617</v>
+        <v>0.1007515382256947</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.03680306060474948</v>
+        <v>-0.05194471791866876</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.07219062891801813</v>
+        <v>-0.1080748029034613</v>
       </c>
       <c r="FL8" t="n">
         <v>0</v>
       </c>
       <c r="FM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
         <v>0</v>
@@ -4929,16 +4929,16 @@
         <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.01476737122975647</v>
+        <v>-0.001529159638649118</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.004897372412560036</v>
+        <v>0.01314320059438252</v>
       </c>
       <c r="FT8" t="n">
-        <v>-0.08033990727461443</v>
+        <v>0.08915713241354549</v>
       </c>
       <c r="FU8" t="n">
         <v>0</v>
@@ -4947,28 +4947,28 @@
         <v>0</v>
       </c>
       <c r="FW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX8" t="n">
         <v>0</v>
       </c>
       <c r="FY8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.02414975868962727</v>
+        <v>0.07328541694129881</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.05237701230296286</v>
+        <v>-0.05808592165021172</v>
       </c>
       <c r="GC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE8" t="n">
         <v>0</v>
@@ -4977,7 +4977,7 @@
         <v>-0</v>
       </c>
       <c r="GG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="9">
@@ -5551,25 +5551,25 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.264104625073795</v>
+        <v>0.3307934185071967</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2485206480820467</v>
+        <v>-0.05422847327849794</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.07897284315129049</v>
+        <v>-0.1510762532647698</v>
       </c>
       <c r="G10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>-0</v>
@@ -5581,7 +5581,7 @@
         <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1688855793614725</v>
+        <v>0.4160656197326677</v>
       </c>
       <c r="L10" t="n">
         <v>-0</v>
@@ -5590,13 +5590,13 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2128006195205676</v>
+        <v>-0.1239861065880381</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.07699486986944411</v>
+        <v>-0.1254106392777468</v>
       </c>
       <c r="P10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -5605,10 +5605,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.05384214227774273</v>
+        <v>0.1042950426429706</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
@@ -5617,37 +5617,37 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.007068793120413116</v>
+        <v>-0.08778493393604232</v>
       </c>
       <c r="X10" t="n">
-        <v>0.05248474377731115</v>
+        <v>-0.003276255899148788</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB10" t="n">
         <v>-0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.05601186978547228</v>
+        <v>-0.05354237406313005</v>
       </c>
       <c r="AD10" t="n">
         <v>-0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.0008421390309708468</v>
+        <v>-0.2056676728522598</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.02098032394674807</v>
+        <v>0.02173324163838832</v>
       </c>
       <c r="AH10" t="n">
         <v>-0</v>
@@ -5659,25 +5659,25 @@
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.06584566905399772</v>
+        <v>0.05001448305696769</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.0264635322808543</v>
+        <v>-0.05427838020683157</v>
       </c>
       <c r="AP10" t="n">
-        <v>-0.02738350104291321</v>
+        <v>-0.04603844432134944</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR10" t="n">
         <v>-0</v>
@@ -5686,10 +5686,10 @@
         <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.2398112073660101</v>
+        <v>0.4338011342949238</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -5698,121 +5698,121 @@
         <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.09960808047690846</v>
+        <v>-0.1984727910486669</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0.04393254093621919</v>
+        <v>-0.1482825315156203</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
       </c>
       <c r="BC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.05320484120239224</v>
+        <v>-0.06192155669277613</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.1440074718833448</v>
+        <v>-0.06899175384968433</v>
       </c>
       <c r="BH10" t="n">
-        <v>-0.03501795472371914</v>
+        <v>0.001621303791001236</v>
       </c>
       <c r="BI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.1201893222188195</v>
+        <v>0.1051417679592239</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO10" t="n">
         <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.05447646155789462</v>
+        <v>0.1276236792023528</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.05867082401031431</v>
+        <v>0.05900589040422697</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU10" t="n">
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.1614555222821348</v>
+        <v>0.3158672971076314</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
         <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.05410170195217793</v>
+        <v>-0.06849647130489755</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.03124340784275591</v>
+        <v>-0.06306188202970338</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC10" t="n">
         <v>-0</v>
       </c>
       <c r="CD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.04369039506199975</v>
+        <v>-0.1096463334498849</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.03912762188810325</v>
+        <v>0.05128570117603581</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.03009578347315211</v>
+        <v>0.05719291783130101</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
         <v>0</v>
@@ -5824,7 +5824,7 @@
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.04934661257828325</v>
+        <v>-0.2107971161781302</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
@@ -5833,10 +5833,10 @@
         <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.02447368689268535</v>
+        <v>0.2111086891727429</v>
       </c>
       <c r="CR10" t="n">
-        <v>-0.01642757211690539</v>
+        <v>0.00683972686440892</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
@@ -5845,25 +5845,25 @@
         <v>-0</v>
       </c>
       <c r="CU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.02396535172223286</v>
+        <v>-0.1003206229483969</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
         <v>0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.03775246226485882</v>
+        <v>0.02630604791695</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.03885568045665938</v>
+        <v>0.06700167249836664</v>
       </c>
       <c r="DB10" t="n">
         <v>0</v>
@@ -5878,46 +5878,46 @@
         <v>-0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.0498175210965279</v>
+        <v>-0.08670924260656498</v>
       </c>
       <c r="DG10" t="n">
         <v>-0</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.02322863544493467</v>
+        <v>-0.0516316664566537</v>
       </c>
       <c r="DJ10" t="n">
-        <v>-0.006994415250422894</v>
+        <v>-0.01790547203355184</v>
       </c>
       <c r="DK10" t="n">
         <v>0</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.04086519685561452</v>
+        <v>-0.05661953281497148</v>
       </c>
       <c r="DP10" t="n">
         <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.01108480743143204</v>
+        <v>0.00241266668176412</v>
       </c>
       <c r="DS10" t="n">
-        <v>-0.0736582169766235</v>
+        <v>-0.02898360911324354</v>
       </c>
       <c r="DT10" t="n">
         <v>-0</v>
@@ -5929,49 +5929,49 @@
         <v>-0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.01134840012347977</v>
+        <v>0.03921855582786685</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.05827830801922173</v>
+        <v>-0.01775362765036817</v>
       </c>
       <c r="EB10" t="n">
-        <v>-0.05428962223870487</v>
+        <v>0.02883271408860908</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE10" t="n">
         <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.01808937818251577</v>
+        <v>-0.03364054517518438</v>
       </c>
       <c r="EH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.04582591772550092</v>
+        <v>-0.005223213498974016</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.01822300866276186</v>
+        <v>0.06076722395403932</v>
       </c>
       <c r="EL10" t="n">
         <v>-0</v>
@@ -5980,28 +5980,28 @@
         <v>-0</v>
       </c>
       <c r="EN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.03883334282360606</v>
+        <v>-0.01578239146452388</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER10" t="n">
         <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.01856368538874706</v>
+        <v>-0.08181356410326611</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.05763376540731399</v>
+        <v>0.03922086672333659</v>
       </c>
       <c r="EU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV10" t="n">
         <v>0</v>
@@ -6010,55 +6010,55 @@
         <v>0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.01726274255845798</v>
+        <v>-0.1253773650254132</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA10" t="n">
         <v>-0</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.0324700355103799</v>
+        <v>0.03157155336469691</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.04282637791204649</v>
+        <v>0.04560045050416361</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF10" t="n">
         <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.05403354787733576</v>
+        <v>-0.1015410953374303</v>
       </c>
       <c r="FI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ10" t="n">
         <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.04110240189413623</v>
+        <v>0.1279576349795438</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.02431927888873728</v>
+        <v>-0.003835154234602305</v>
       </c>
       <c r="FM10" t="n">
         <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO10" t="n">
         <v>0</v>
@@ -6067,34 +6067,34 @@
         <v>0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.005092202056443456</v>
+        <v>0.01193116313725316</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS10" t="n">
         <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.008546582290248636</v>
+        <v>-0.01959976543698199</v>
       </c>
       <c r="FU10" t="n">
-        <v>-0.001242687480695364</v>
+        <v>0.007565546054101027</v>
       </c>
       <c r="FV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.05508977738550464</v>
+        <v>-0.1013088202767404</v>
       </c>
       <c r="GA10" t="n">
         <v>0</v>
@@ -6103,10 +6103,10 @@
         <v>-0</v>
       </c>
       <c r="GC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0.0459809164027562</v>
+        <v>0.08548908091673102</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
@@ -6115,7 +6115,7 @@
         <v>-0</v>
       </c>
       <c r="GG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="11">
@@ -6123,22 +6123,22 @@
         <v>-0</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.442382249433143</v>
+        <v>-0.5497237947075514</v>
       </c>
       <c r="C11" t="n">
         <v>-0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3747995993462746</v>
+        <v>0.3548241188338968</v>
       </c>
       <c r="E11" t="n">
-        <v>0.06651023835555633</v>
+        <v>0.2513267847458222</v>
       </c>
       <c r="F11" t="n">
         <v>-0</v>
       </c>
       <c r="G11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -6150,25 +6150,25 @@
         <v>-0</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3198233993159657</v>
+        <v>-0.5315340851484915</v>
       </c>
       <c r="L11" t="n">
         <v>-0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3427104479341317</v>
+        <v>0.4673596663637167</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1208805407141284</v>
+        <v>0.3013077306765666</v>
       </c>
       <c r="O11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>-0</v>
@@ -6177,103 +6177,103 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.060837581699869</v>
+        <v>-0.06739374245555421</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0.09337584099454896</v>
+        <v>0.07086873976620704</v>
       </c>
       <c r="W11" t="n">
-        <v>0.03387214980602345</v>
+        <v>0.008390945063443138</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>-0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.05427026463074897</v>
+        <v>-0.02651974764476659</v>
       </c>
       <c r="AD11" t="n">
         <v>-0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.005882682600939535</v>
+        <v>0.1057842650068584</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.01579804246694199</v>
+        <v>0.05625821271243311</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.07918641762737882</v>
+        <v>-0.2582139497090295</v>
       </c>
       <c r="AM11" t="n">
         <v>-0</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.006403671640698059</v>
+        <v>0.04089550211087831</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.04460325771461742</v>
+        <v>-0.1739657780958425</v>
       </c>
       <c r="AP11" t="n">
         <v>-0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
         <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>-0.3216079518057502</v>
+        <v>-0.4614591456511667</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.1251110557586896</v>
+        <v>0.07299533618253996</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.01998069808896589</v>
+        <v>0.1735740673251996</v>
       </c>
       <c r="AY11" t="n">
         <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA11" t="n">
         <v>-0</v>
@@ -6285,25 +6285,25 @@
         <v>-0</v>
       </c>
       <c r="BD11" t="n">
-        <v>-0.02523909472222382</v>
+        <v>0.1298833014356302</v>
       </c>
       <c r="BE11" t="n">
         <v>-0</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.1592216421799026</v>
+        <v>0.1945314672146261</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.253488278599699</v>
+        <v>0.2272388733565172</v>
       </c>
       <c r="BH11" t="n">
         <v>-0</v>
       </c>
       <c r="BI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK11" t="n">
         <v>-0</v>
@@ -6312,25 +6312,25 @@
         <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.006113677122042046</v>
+        <v>0.03819725456807749</v>
       </c>
       <c r="BN11" t="n">
         <v>0</v>
       </c>
       <c r="BO11" t="n">
-        <v>-0.01084323145018735</v>
+        <v>-0.05909256053071761</v>
       </c>
       <c r="BP11" t="n">
-        <v>-0.05747526036399998</v>
+        <v>-0.01627741225801875</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT11" t="n">
         <v>0</v>
@@ -6339,19 +6339,19 @@
         <v>0</v>
       </c>
       <c r="BV11" t="n">
-        <v>-0.2549898676879342</v>
+        <v>-0.4703762541690169</v>
       </c>
       <c r="BW11" t="n">
         <v>-0</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.1279045257946712</v>
+        <v>0.1484887960678272</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.01797495143687422</v>
+        <v>0.06830268765839637</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA11" t="n">
         <v>0</v>
@@ -6363,19 +6363,19 @@
         <v>-0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.08241687855633757</v>
+        <v>0.2478075108282689</v>
       </c>
       <c r="CF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG11" t="n">
-        <v>-0.07103931190142759</v>
+        <v>-0.1278796084073565</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.03648375222765497</v>
+        <v>-0.02546596983910989</v>
       </c>
       <c r="CI11" t="n">
         <v>0</v>
@@ -6393,19 +6393,19 @@
         <v>-0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.03733395568155085</v>
+        <v>0.2775895316612162</v>
       </c>
       <c r="CO11" t="n">
         <v>0</v>
       </c>
       <c r="CP11" t="n">
-        <v>-0.07767144792694908</v>
+        <v>-0.2862737570959672</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.01794562867111722</v>
+        <v>-0.194524536171392</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS11" t="n">
         <v>0</v>
@@ -6417,19 +6417,19 @@
         <v>0</v>
       </c>
       <c r="CV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.08285921797611127</v>
+        <v>0.2442755290669925</v>
       </c>
       <c r="CX11" t="n">
         <v>-0</v>
       </c>
       <c r="CY11" t="n">
-        <v>-0.06728278254238276</v>
+        <v>-0.1404055720636057</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.0033653874995146</v>
+        <v>-0.05280071272499034</v>
       </c>
       <c r="DA11" t="n">
         <v>-0</v>
@@ -6444,22 +6444,22 @@
         <v>-0</v>
       </c>
       <c r="DE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.1119811808794673</v>
+        <v>0.1274229537042183</v>
       </c>
       <c r="DG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH11" t="n">
-        <v>-0.03190294314502466</v>
+        <v>-0.03337458734722127</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.01289305448750696</v>
+        <v>0.02199641784398402</v>
       </c>
       <c r="DJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
@@ -6468,55 +6468,55 @@
         <v>-0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.06898532762388809</v>
+        <v>0.1344667786901357</v>
       </c>
       <c r="DP11" t="n">
         <v>0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0.1001153315500573</v>
+        <v>-0.02937906182449642</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.07751297470501176</v>
+        <v>0.05101103314636377</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV11" t="n">
         <v>-0</v>
       </c>
       <c r="DW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.01195631187899207</v>
+        <v>-0.02670619906376621</v>
       </c>
       <c r="DY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.05562582753999609</v>
+        <v>0.07838214627180853</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.02235360264038659</v>
+        <v>-0.07816157527157165</v>
       </c>
       <c r="EB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED11" t="n">
         <v>-0</v>
@@ -6525,52 +6525,52 @@
         <v>0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.004794078675077203</v>
+        <v>0.2322213801148917</v>
       </c>
       <c r="EH11" t="n">
         <v>-0</v>
       </c>
       <c r="EI11" t="n">
-        <v>-0.04772513083821293</v>
+        <v>-0.1310946000984627</v>
       </c>
       <c r="EJ11" t="n">
-        <v>-0.01775137187064316</v>
+        <v>-0.05717097955429461</v>
       </c>
       <c r="EK11" t="n">
         <v>0</v>
       </c>
       <c r="EL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.1069167440826389</v>
+        <v>0.1711358655601567</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.005774816637704035</v>
+        <v>-0.1055350929601948</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.03859785505239472</v>
+        <v>-0.08993794336367379</v>
       </c>
       <c r="ET11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV11" t="n">
         <v>-0</v>
@@ -6579,19 +6579,19 @@
         <v>0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.09632321230935817</v>
+        <v>0.2979377593355579</v>
       </c>
       <c r="EZ11" t="n">
         <v>0</v>
       </c>
       <c r="FA11" t="n">
-        <v>-0.08918025267885014</v>
+        <v>-0.147536783753946</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.0198680724538197</v>
+        <v>-0.05257817218849665</v>
       </c>
       <c r="FC11" t="n">
         <v>0</v>
@@ -6609,79 +6609,79 @@
         <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.02687333462369916</v>
+        <v>0.1388330833043309</v>
       </c>
       <c r="FI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ11" t="n">
-        <v>-0.01436673918717214</v>
+        <v>-0.04967592080729211</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.02489312972164674</v>
+        <v>-0.0251328141350852</v>
       </c>
       <c r="FL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN11" t="n">
         <v>-0</v>
       </c>
       <c r="FO11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.004364323393124556</v>
+        <v>-0.008864560465268486</v>
       </c>
       <c r="FR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS11" t="n">
-        <v>-0.03347795829537985</v>
+        <v>-0.04339117988431198</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.0002360877417290831</v>
+        <v>-0.01099600229774165</v>
       </c>
       <c r="FU11" t="n">
         <v>0</v>
       </c>
       <c r="FV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
         <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.06398936262561127</v>
+        <v>0.2266569197649947</v>
       </c>
       <c r="GA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.08609539800691976</v>
+        <v>-0.06997621385370466</v>
       </c>
       <c r="GC11" t="n">
         <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE11" t="n">
         <v>0</v>
       </c>
       <c r="GF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG11" t="n">
         <v>0</v>
@@ -6692,43 +6692,43 @@
         <v>-0</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.770513474194241</v>
+        <v>-0.509049208633081</v>
       </c>
       <c r="C12" t="n">
         <v>-0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5584190239180331</v>
+        <v>0.3215359052335275</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.001546201939027836</v>
+        <v>0.07743754075244437</v>
       </c>
       <c r="F12" t="n">
         <v>-0</v>
       </c>
       <c r="G12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5758384597554235</v>
+        <v>-0.4354494544947507</v>
       </c>
       <c r="L12" t="n">
         <v>-0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4954384386152756</v>
+        <v>0.5558966085499559</v>
       </c>
       <c r="N12" t="n">
-        <v>0.08014584078809472</v>
+        <v>0.2241117047083983</v>
       </c>
       <c r="O12" t="n">
         <v>-0</v>
@@ -6737,34 +6737,34 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1195432959027974</v>
+        <v>-0.07204644653387639</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1234766840388874</v>
+        <v>0.09146219267817628</v>
       </c>
       <c r="W12" t="n">
-        <v>0.133021201234866</v>
+        <v>0.04781183676438407</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>-0</v>
@@ -6773,22 +6773,22 @@
         <v>-0</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.148964921156541</v>
+        <v>-0.05633353208511219</v>
       </c>
       <c r="AD12" t="n">
         <v>-0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.06547974011308851</v>
+        <v>0.1667342160179028</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.09842372966227569</v>
+        <v>0.1322862307010053</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -6797,28 +6797,28 @@
         <v>-0</v>
       </c>
       <c r="AK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.1294625009305195</v>
+        <v>-0.1645032544814654</v>
       </c>
       <c r="AM12" t="n">
         <v>-0</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.05892446017983981</v>
+        <v>0.01607050230741722</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.05452792567984467</v>
+        <v>-0.06635259347790914</v>
       </c>
       <c r="AP12" t="n">
         <v>-0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
         <v>-0</v>
@@ -6827,22 +6827,22 @@
         <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>-0.4010295643401878</v>
+        <v>-0.2942391466054142</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.181603368389571</v>
+        <v>0.02579470593550881</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.04961249060251804</v>
+        <v>0.2606072622418221</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
         <v>0</v>
@@ -6854,16 +6854,16 @@
         <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>-0.07298821020661865</v>
+        <v>0.009092584882294462</v>
       </c>
       <c r="BE12" t="n">
         <v>-0</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.1470505344040834</v>
+        <v>0.2041726167729192</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.206431787515752</v>
+        <v>0.08012414665345323</v>
       </c>
       <c r="BH12" t="n">
         <v>-0</v>
@@ -6872,7 +6872,7 @@
         <v>0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK12" t="n">
         <v>-0</v>
@@ -6881,22 +6881,22 @@
         <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>-0.1197126936066577</v>
+        <v>-0.1465919839804687</v>
       </c>
       <c r="BN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO12" t="n">
-        <v>-0.1121177769058646</v>
+        <v>-0.04890014125166085</v>
       </c>
       <c r="BP12" t="n">
-        <v>-0.04616492631513487</v>
+        <v>-0.05831192870472595</v>
       </c>
       <c r="BQ12" t="n">
         <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
@@ -6908,22 +6908,22 @@
         <v>0</v>
       </c>
       <c r="BV12" t="n">
-        <v>-0.3934003966893388</v>
+        <v>-0.3551014763635592</v>
       </c>
       <c r="BW12" t="n">
         <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.1970108997058102</v>
+        <v>0.1078830705984997</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.004986210057598064</v>
+        <v>0.04649728744175174</v>
       </c>
       <c r="BZ12" t="n">
         <v>-0</v>
       </c>
       <c r="CA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB12" t="n">
         <v>-0</v>
@@ -6935,22 +6935,22 @@
         <v>0</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.1191644594890167</v>
+        <v>0.1491323353903605</v>
       </c>
       <c r="CF12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG12" t="n">
-        <v>-0.09587585485212861</v>
+        <v>-0.08445798382495755</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.0400349699326466</v>
+        <v>-0.008842287393695948</v>
       </c>
       <c r="CI12" t="n">
         <v>0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK12" t="n">
         <v>-0</v>
@@ -6962,19 +6962,19 @@
         <v>-0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.01368319867576999</v>
+        <v>0.08250005604427238</v>
       </c>
       <c r="CO12" t="n">
         <v>0</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.03329915683221254</v>
+        <v>-0.1126608553983028</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.06609019375686949</v>
+        <v>-0.1839593172301319</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
         <v>0</v>
@@ -6983,28 +6983,28 @@
         <v>0</v>
       </c>
       <c r="CU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.1265654154199616</v>
+        <v>0.1176619546468377</v>
       </c>
       <c r="CX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY12" t="n">
-        <v>-0.1219826734584444</v>
+        <v>-0.104504223937135</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.04411738645394709</v>
+        <v>-0.03249249407643356</v>
       </c>
       <c r="DA12" t="n">
         <v>-0</v>
       </c>
       <c r="DB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC12" t="n">
         <v>0</v>
@@ -7016,52 +7016,52 @@
         <v>-0</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.08576873498947099</v>
+        <v>0.01578844930009649</v>
       </c>
       <c r="DG12" t="n">
         <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>-0.1952283225302615</v>
+        <v>-0.05101891478807127</v>
       </c>
       <c r="DI12" t="n">
-        <v>-0.01656502080716098</v>
+        <v>0.02695783316991631</v>
       </c>
       <c r="DJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN12" t="n">
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.05657241151899162</v>
+        <v>0.21772647994897</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0.02906567094357025</v>
+        <v>0.03205427217471171</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.06646119740743489</v>
+        <v>-0.09787085518708845</v>
       </c>
       <c r="DS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV12" t="n">
         <v>-0</v>
@@ -7070,25 +7070,25 @@
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.1344902793679884</v>
+        <v>-0.03241023267942627</v>
       </c>
       <c r="DY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.09860548440401791</v>
+        <v>0.04310557195461603</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.004026901749638948</v>
+        <v>-0.01169715556742907</v>
       </c>
       <c r="EB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC12" t="n">
         <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
         <v>0</v>
@@ -7097,16 +7097,16 @@
         <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.04066509336699618</v>
+        <v>0.04489669451923305</v>
       </c>
       <c r="EH12" t="n">
         <v>-0</v>
       </c>
       <c r="EI12" t="n">
-        <v>-0.06032274545075186</v>
+        <v>-0.1078037765656001</v>
       </c>
       <c r="EJ12" t="n">
-        <v>-0.0119944933285821</v>
+        <v>0.05782250075274886</v>
       </c>
       <c r="EK12" t="n">
         <v>0</v>
@@ -7115,58 +7115,58 @@
         <v>0</v>
       </c>
       <c r="EM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.1386616596901079</v>
+        <v>0.1237162000482087</v>
       </c>
       <c r="EQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER12" t="n">
-        <v>-0.07281171680567951</v>
+        <v>-0.08593651248952094</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.009047663553885246</v>
+        <v>0.02775705382820858</v>
       </c>
       <c r="ET12" t="n">
         <v>0</v>
       </c>
       <c r="EU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV12" t="n">
         <v>-0</v>
       </c>
       <c r="EW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.1179812924171284</v>
+        <v>0.1718419195106008</v>
       </c>
       <c r="EZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA12" t="n">
-        <v>-0.128705765070022</v>
+        <v>-0.07908130834126618</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.05135715373767621</v>
+        <v>-0.007226887932375124</v>
       </c>
       <c r="FC12" t="n">
         <v>0</v>
       </c>
       <c r="FD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE12" t="n">
         <v>-0</v>
@@ -7175,85 +7175,85 @@
         <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.06331671133442181</v>
+        <v>0.01386764636418492</v>
       </c>
       <c r="FI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>-0.05196123262397379</v>
+        <v>-0.103630669517575</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.01398030333586952</v>
+        <v>0.04758484136421565</v>
       </c>
       <c r="FL12" t="n">
         <v>0</v>
       </c>
       <c r="FM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP12" t="n">
         <v>0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.04028311034348863</v>
+        <v>-0.02196068683098594</v>
       </c>
       <c r="FR12" t="n">
         <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.03183581492907049</v>
+        <v>0.001309175101589556</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.03227688320287642</v>
+        <v>-0.001880617801786272</v>
       </c>
       <c r="FU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW12" t="n">
         <v>-0</v>
       </c>
       <c r="FX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.01451143983814998</v>
+        <v>0.04387107633741363</v>
       </c>
       <c r="GA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.03961548978245614</v>
+        <v>-0.01639502245061494</v>
       </c>
       <c r="GC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE12" t="n">
         <v>0</v>
       </c>
       <c r="GF12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,16 +7261,16 @@
         <v>-0</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.237050161342131</v>
+        <v>-0.5258552730639625</v>
       </c>
       <c r="C13" t="n">
         <v>-0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3264091191912683</v>
+        <v>0.454840003312945</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.01334948767833292</v>
+        <v>0.2760999477102937</v>
       </c>
       <c r="F13" t="n">
         <v>-0</v>
@@ -7279,7 +7279,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>-0</v>
@@ -7288,124 +7288,124 @@
         <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1216481109166054</v>
+        <v>-0.4312567937635068</v>
       </c>
       <c r="L13" t="n">
         <v>-0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2970897122750605</v>
+        <v>0.6231335038528211</v>
       </c>
       <c r="N13" t="n">
-        <v>0.01883587870668917</v>
+        <v>0.2962449143085533</v>
       </c>
       <c r="O13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>-0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.04591712628129267</v>
+        <v>-0.06793053985459069</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>0.06019554962637719</v>
+        <v>0.1242829110372272</v>
       </c>
       <c r="W13" t="n">
-        <v>0.002886326374521131</v>
+        <v>0.002724961141126477</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>-0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.01164374053241764</v>
+        <v>0.01304095221139181</v>
       </c>
       <c r="AD13" t="n">
         <v>-0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.01785233748883714</v>
+        <v>0.01480885662299998</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.01831993563582293</v>
+        <v>-0.07931680399244966</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
         <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>-0.02483397491129846</v>
+        <v>-0.1877037965802469</v>
       </c>
       <c r="AM13" t="n">
         <v>-0</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.06188651108657639</v>
+        <v>0.07761240276482434</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.05672723402563085</v>
+        <v>-0.2058740011795393</v>
       </c>
       <c r="AP13" t="n">
         <v>-0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
         <v>-0</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU13" t="n">
-        <v>-0.2084285070325546</v>
+        <v>-0.4808374892009107</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.09276646746983967</v>
+        <v>0.1513564730253658</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.0431980227255577</v>
+        <v>0.05036331711261018</v>
       </c>
       <c r="AY13" t="n">
         <v>0</v>
@@ -7414,106 +7414,106 @@
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>-0.003281314998267222</v>
+        <v>0.0616750686426266</v>
       </c>
       <c r="BE13" t="n">
         <v>-0</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.1218544521296967</v>
+        <v>0.1394289344394202</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.1249774854563081</v>
+        <v>0.2568688930572096</v>
       </c>
       <c r="BH13" t="n">
         <v>-0</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL13" t="n">
         <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>-0.03637210217549814</v>
+        <v>0.07749573402077135</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
-        <v>-0.01876659517638418</v>
+        <v>-0.0776978475618106</v>
       </c>
       <c r="BP13" t="n">
-        <v>-0.08928586288099404</v>
+        <v>-0.03959519717552794</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS13" t="n">
         <v>0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
         <v>0</v>
       </c>
       <c r="BV13" t="n">
-        <v>-0.1004864921060331</v>
+        <v>-0.399349274497838</v>
       </c>
       <c r="BW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.02890188888327556</v>
+        <v>0.2058888424093286</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.0228788068493051</v>
+        <v>0.00901016603763153</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA13" t="n">
         <v>0</v>
       </c>
       <c r="CB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD13" t="n">
         <v>0</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.0415210043002123</v>
+        <v>0.261632363652009</v>
       </c>
       <c r="CF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0.05362939091512686</v>
+        <v>-0.1231155242763609</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.03738118405341904</v>
+        <v>-0.02079429793360094</v>
       </c>
       <c r="CI13" t="n">
         <v>0</v>
@@ -7525,25 +7525,25 @@
         <v>-0</v>
       </c>
       <c r="CL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM13" t="n">
         <v>-0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.06170760578213239</v>
+        <v>0.2901293863971396</v>
       </c>
       <c r="CO13" t="n">
         <v>0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.04279557761137583</v>
+        <v>-0.2431877700363834</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.0297722077654516</v>
+        <v>-0.05325438866120809</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS13" t="n">
         <v>0</v>
@@ -7552,22 +7552,22 @@
         <v>0</v>
       </c>
       <c r="CU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.04407291897571493</v>
+        <v>0.2657422991807792</v>
       </c>
       <c r="CX13" t="n">
         <v>-0</v>
       </c>
       <c r="CY13" t="n">
-        <v>-0.05332385520707417</v>
+        <v>-0.1361895357298893</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.0175764224989942</v>
+        <v>-0.04841319380238286</v>
       </c>
       <c r="DA13" t="n">
         <v>-0</v>
@@ -7579,22 +7579,22 @@
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.004432617258273545</v>
+        <v>-0.005354170628222348</v>
       </c>
       <c r="DG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0.0259033686607053</v>
+        <v>-0.03138574383343046</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.02850397755753761</v>
+        <v>-0.02055778743849621</v>
       </c>
       <c r="DJ13" t="n">
         <v>0</v>
@@ -7609,28 +7609,28 @@
         <v>-0</v>
       </c>
       <c r="DN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.02432052914685516</v>
+        <v>0.1329122131901139</v>
       </c>
       <c r="DP13" t="n">
         <v>0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.03786080008191293</v>
+        <v>0.02920447216835667</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.001010262279791043</v>
+        <v>0.0412262089960633</v>
       </c>
       <c r="DS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT13" t="n">
         <v>0</v>
       </c>
       <c r="DU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV13" t="n">
         <v>-0</v>
@@ -7639,76 +7639,76 @@
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.01771801974101739</v>
+        <v>-0.0709371809416388</v>
       </c>
       <c r="DY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0.01247983222390304</v>
+        <v>-0.05692145718961624</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.01007704819315889</v>
+        <v>-0.07280514972665486</v>
       </c>
       <c r="EB13" t="n">
         <v>0</v>
       </c>
       <c r="EC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED13" t="n">
         <v>-0</v>
       </c>
       <c r="EE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF13" t="n">
         <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.01525103194310808</v>
+        <v>0.2452846043754564</v>
       </c>
       <c r="EH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI13" t="n">
-        <v>-0.03385209342539683</v>
+        <v>-0.07158709453483807</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.003515375788503973</v>
+        <v>-0.1059407605176825</v>
       </c>
       <c r="EK13" t="n">
         <v>0</v>
       </c>
       <c r="EL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO13" t="n">
         <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.03733688304514752</v>
+        <v>0.1703047319668129</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.00384055230125505</v>
+        <v>-0.126645330192704</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.001147125115477005</v>
+        <v>-0.08250827302756035</v>
       </c>
       <c r="ET13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV13" t="n">
         <v>-0</v>
@@ -7717,19 +7717,19 @@
         <v>0</v>
       </c>
       <c r="EX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.04342617232110002</v>
+        <v>0.3031181875399713</v>
       </c>
       <c r="EZ13" t="n">
         <v>0</v>
       </c>
       <c r="FA13" t="n">
-        <v>-0.04486585658349346</v>
+        <v>-0.1696020971732831</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.02080317511084892</v>
+        <v>-0.03081824785802158</v>
       </c>
       <c r="FC13" t="n">
         <v>0</v>
@@ -7741,73 +7741,73 @@
         <v>-0</v>
       </c>
       <c r="FF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG13" t="n">
         <v>-0</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.01862471264788797</v>
+        <v>0.1412907714991036</v>
       </c>
       <c r="FI13" t="n">
         <v>0</v>
       </c>
       <c r="FJ13" t="n">
-        <v>-0.03350520536153774</v>
+        <v>-0.1364787594480237</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.008675828222694386</v>
+        <v>-0.01545629533989091</v>
       </c>
       <c r="FL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM13" t="n">
         <v>-0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP13" t="n">
         <v>0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.003137016398846191</v>
+        <v>-0.04204076600767922</v>
       </c>
       <c r="FR13" t="n">
         <v>0</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.008975647927561359</v>
+        <v>-0.1215167010840522</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.006195530780974849</v>
+        <v>0.009067495842206933</v>
       </c>
       <c r="FU13" t="n">
         <v>0</v>
       </c>
       <c r="FV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
         <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.01706859654302902</v>
+        <v>0.1898653132285395</v>
       </c>
       <c r="GA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.07005085678739789</v>
+        <v>-0.05388575870053879</v>
       </c>
       <c r="GC13" t="n">
         <v>-0</v>
@@ -7819,7 +7819,7 @@
         <v>0</v>
       </c>
       <c r="GF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG13" t="n">
         <v>0</v>
